--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AT ELGA e-Medikation medication Medikation</t>
+    <t>AT ELGA e-Medikation Medication Medikation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,7 +689,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-substanz) &lt;&lt;contained&gt;&gt;</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff) &lt;&lt;contained&gt;&gt;</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -726,7 +726,7 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-substanz) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -1155,7 +1155,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="90.80859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="90.55859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:37:50+00:00</t>
+    <t>2026-06-15T21:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe.</t>
+    <t>Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, Geplanter Abgabe und Durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
